--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6197-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6197-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EA45678-B2CC-4E31-BB59-0C564C614E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DBE0048-86AE-4108-9511-B425530BF38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{6C081012-F223-42E8-B775-5455ABA23E49}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{5165F8F0-0D15-4B32-907A-430D822140EB}"/>
   </bookViews>
   <sheets>
     <sheet name="6197-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1517,26 +1517,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EDAB6D-5B4E-4A73-A5C2-12B0AD9DDB18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725F4A03-965A-4C08-B391-FF7ABA73726D}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1726,7 +1726,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>30</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>30</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>30</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2022</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>30</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2021</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>30</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>30</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2020</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>30</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2019</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>30</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>30</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2018</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2017</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2016</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2015</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>8.0500000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2014</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2013</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2012</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2011</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2010</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2009</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2008</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2007</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2006</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2005</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2004</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2003</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2002</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2001</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2000</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
         <v>60</v>
       </c>
